--- a/data/dividends_info_20261015.xlsx
+++ b/data/dividends_info_20261015.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>39.89500045776367</v>
+        <v>41.40999984741211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2255921768826193</v>
+        <v>0.2173388078522886</v>
       </c>
       <c r="J2" t="n">
         <v>151</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>60.95000076293945</v>
+        <v>60.70000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.148482348216202</v>
+        <v>1.153212506098331</v>
       </c>
       <c r="J3" t="n">
         <v>130</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.779999732971191</v>
+        <v>8.840000152587891</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6833713191890466</v>
+        <v>0.6787330199585475</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39.89500045776367</v>
+        <v>41.40999984741211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2255921768826193</v>
+        <v>0.2173388078522886</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>51.25</v>
+        <v>51.79999923706055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6048780487804878</v>
+        <v>0.5984556072699883</v>
       </c>
       <c r="J8" t="n">
         <v>39</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>25.77000045776367</v>
+        <v>25.77499961853027</v>
       </c>
       <c r="I9" t="n">
-        <v>1.047729899898615</v>
+        <v>1.047526688636265</v>
       </c>
       <c r="J9" t="n">
         <v>39</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25.76000022888184</v>
+        <v>25.65999984741211</v>
       </c>
       <c r="I10" t="n">
-        <v>2.290372650457116</v>
+        <v>2.29929853276871</v>
       </c>
       <c r="J10" t="n">
         <v>39</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.47999954223633</v>
+        <v>10.61999988555908</v>
       </c>
       <c r="I11" t="n">
-        <v>2.00381688141933</v>
+        <v>1.97740115125194</v>
       </c>
       <c r="J11" t="n">
         <v>32</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.989999771118164</v>
+        <v>6.03000020980835</v>
       </c>
       <c r="I12" t="n">
-        <v>3.338898291187508</v>
+        <v>3.31674947000303</v>
       </c>
       <c r="J12" t="n">
         <v>32</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7.989999771118164</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7509386948530947</v>
+        <v>0.7425742644373664</v>
       </c>
       <c r="J14" t="n">
         <v>25</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.56999969482422</v>
+        <v>10.61999988555908</v>
       </c>
       <c r="I15" t="n">
-        <v>4.351939576925881</v>
+        <v>4.331450140837583</v>
       </c>
       <c r="J15" t="n">
         <v>11</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8.300000190734863</v>
+        <v>8.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4578313147801936</v>
+        <v>0.4470588235294118</v>
       </c>
       <c r="J19" t="n">
         <v>-17</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.965999960899353</v>
+        <v>1.942999958992004</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8992879518637</v>
+        <v>2.93360788486947</v>
       </c>
       <c r="J21" t="n">
         <v>-24</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.89500045776367</v>
+        <v>41.40999984741211</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2255921768826193</v>
+        <v>0.2173388078522886</v>
       </c>
       <c r="J22" t="n">
         <v>-24</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>92.5</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="I23" t="n">
-        <v>1.437837837837838</v>
+        <v>1.436285120859581</v>
       </c>
       <c r="J23" t="n">
         <v>-24</v>
@@ -1777,7 +1777,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1804,14 +1804,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1828,7 +1828,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1838,14 +1838,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1862,7 +1862,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1906,14 +1906,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2110,14 +2110,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2127,14 +2127,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2144,14 +2144,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2185,7 +2185,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2195,14 +2195,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2212,14 +2212,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2236,7 +2236,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2263,14 +2263,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2287,7 +2287,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2331,14 +2331,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2348,14 +2348,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2372,7 +2372,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2399,14 +2399,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2433,14 +2433,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2450,14 +2450,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2474,7 +2474,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -2501,14 +2501,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2620,14 +2620,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2637,14 +2637,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2729,7 +2729,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2814,7 +2814,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2824,14 +2824,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2858,14 +2858,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2882,7 +2882,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2950,7 +2950,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2960,14 +2960,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2977,14 +2977,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -3011,14 +3011,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3154,7 +3154,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3324,7 +3324,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3334,14 +3334,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3351,14 +3351,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3368,14 +3368,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3402,14 +3402,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3426,7 +3426,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3477,7 +3477,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3504,14 +3504,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3521,14 +3521,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3545,7 +3545,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3562,7 +3562,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3579,7 +3579,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3596,7 +3596,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3606,14 +3606,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3630,7 +3630,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3640,14 +3640,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3664,7 +3664,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3681,7 +3681,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3691,14 +3691,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3708,14 +3708,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3742,14 +3742,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3783,7 +3783,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3827,14 +3827,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3851,7 +3851,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3919,7 +3919,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3936,7 +3936,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3953,7 +3953,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3980,14 +3980,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3997,14 +3997,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4014,14 +4014,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4038,7 +4038,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4055,7 +4055,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4072,7 +4072,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4116,14 +4116,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4133,14 +4133,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4150,14 +4150,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4191,7 +4191,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4225,7 +4225,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4242,7 +4242,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4286,14 +4286,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4327,7 +4327,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4344,7 +4344,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4361,7 +4361,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4371,14 +4371,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4395,7 +4395,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4405,14 +4405,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4422,14 +4422,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4439,14 +4439,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4456,14 +4456,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4480,7 +4480,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4524,14 +4524,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4548,7 +4548,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4565,7 +4565,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4582,7 +4582,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4599,7 +4599,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4616,7 +4616,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4650,7 +4650,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4667,7 +4667,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4684,7 +4684,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4701,7 +4701,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4711,14 +4711,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4728,14 +4728,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4769,7 +4769,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4786,7 +4786,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4820,7 +4820,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4837,7 +4837,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4847,14 +4847,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4871,7 +4871,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4888,7 +4888,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4898,14 +4898,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4915,14 +4915,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4939,7 +4939,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4949,14 +4949,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4966,14 +4966,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4990,7 +4990,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5000,14 +5000,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5058,7 +5058,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5075,7 +5075,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5102,14 +5102,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5143,7 +5143,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5160,7 +5160,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5170,14 +5170,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5194,7 +5194,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5245,7 +5245,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5262,7 +5262,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5272,14 +5272,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5296,7 +5296,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5313,7 +5313,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5330,7 +5330,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5340,14 +5340,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5364,7 +5364,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5381,7 +5381,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5391,14 +5391,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5415,7 +5415,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5432,7 +5432,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5466,7 +5466,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5483,7 +5483,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5500,7 +5500,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5517,7 +5517,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5568,7 +5568,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5578,14 +5578,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5602,7 +5602,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5619,7 +5619,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5653,7 +5653,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5670,7 +5670,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5687,7 +5687,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5704,7 +5704,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5731,14 +5731,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5755,7 +5755,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5772,7 +5772,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5782,14 +5782,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5799,14 +5799,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5816,14 +5816,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5840,7 +5840,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5850,14 +5850,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5874,7 +5874,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5884,14 +5884,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5901,14 +5901,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5918,14 +5918,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5942,7 +5942,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5952,14 +5952,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5986,14 +5986,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6010,7 +6010,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6027,7 +6027,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6037,14 +6037,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6061,7 +6061,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6078,7 +6078,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6116,78 +6116,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Leonardo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Piu' Medical S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>VALSOIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>